--- a/Punctuation/data/subset_puntuation_juez2.xlsx
+++ b/Punctuation/data/subset_puntuation_juez2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esther\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\paula\OTROS\TFG_repo\Punctuation\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9FBEA20-152F-4188-ABAF-AB2A20A6AE06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF114938-AB21-4FB1-B60F-265CF7249B6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4DD2AA4A-FFB2-45BB-AA1D-F63FA651B14A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{4DD2AA4A-FFB2-45BB-AA1D-F63FA651B14A}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="100">
   <si>
     <t>POSITION</t>
   </si>
@@ -61,6 +61,282 @@
   </si>
   <si>
     <t>Knight</t>
+  </si>
+  <si>
+    <t>IMG_1388.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1395.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1398.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1400.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1425.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1427.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1430.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1433.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1434.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1436.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1514.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1519.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1520.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1523.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1266.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1268.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1269.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1271.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1274.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1278.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1279.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1281.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1304.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1306.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1311.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1313.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1316.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1319.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1458.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1459.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1463.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1464.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1467.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1250.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1251.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1253.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1256.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1257.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1260.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1261.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1265.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1287.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1289.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1292.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1294.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1296.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1298.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1300.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1443.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1448.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1449.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1451.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1453.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1322.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1325.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1329.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1330.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1332.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1335.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1337.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1345.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1348.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1351.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1353.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1358.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1477.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1479.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1480.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1482.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1484.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1486.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1487.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1488.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1364.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1365.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1370.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1376.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1377.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1380.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1382.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1386.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1402.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1410.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1414.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1415.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1417.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1492.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1495.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1499.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1501.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1505.JPG</t>
+  </si>
+  <si>
+    <t>IMG_1506.JPG</t>
   </si>
 </sst>
 </file>
@@ -173,7 +449,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -186,6 +462,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -527,14 +804,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1196D214-37D3-4925-9937-9E2D505A232A}">
   <dimension ref="A1:C93"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" customWidth="1"/>
-    <col min="2" max="2" width="20.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="1" max="1" width="31.86328125" customWidth="1"/>
+    <col min="2" max="2" width="20.86328125" customWidth="1"/>
+    <col min="3" max="3" width="19.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -545,1105 +822,1013 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Bent Knee Surface Arch Position\IMG_1388.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B2" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="C2" s="2">
         <v>5.5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Bent Knee Surface Arch Position\IMG_1395.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B3" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="C3" s="2">
         <v>6.6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Bent Knee Surface Arch Position\IMG_1398.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B4" s="12" t="s">
+        <v>10</v>
       </c>
       <c r="C4" s="2">
         <v>7.5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Bent Knee Surface Arch Position\IMG_1400.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B5" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="C5" s="2">
         <v>8.5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="3" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Bent Knee Surface Arch Position\IMG_1425.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B6" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="C6" s="2">
         <v>3.7</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="3" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Bent Knee Surface Arch Position\IMG_1427.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B7" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="C7" s="2">
         <v>5.7</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="3" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Bent Knee Surface Arch Position\IMG_1430.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B8" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C8" s="2">
         <v>5.7</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="3" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Bent Knee Surface Arch Position\IMG_1433.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B9" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="C9" s="2">
         <v>6.4</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="3" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Bent Knee Surface Arch Position\IMG_1434.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B10" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="C10" s="2">
         <v>6.5</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="3" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Bent Knee Surface Arch Position\IMG_1436.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B11" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C11" s="2">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="3" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Bent Knee Surface Arch Position\IMG_1514.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B12" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="C12" s="2">
         <v>4.5</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="3" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Bent Knee Surface Arch Position\IMG_1519.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B13" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="C13" s="2">
         <v>5.6</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="3" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Bent Knee Surface Arch Position\IMG_1520.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B14" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="C14" s="2">
         <v>6.5</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="3" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Bent Knee Surface Arch Position\IMG_1523.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B15" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="C15" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="5" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Bent Knee Vertical\IMG_1266.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B16" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="C16" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="5" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Bent Knee Vertical\IMG_1268.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B17" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="C17" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="5" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Bent Knee Vertical\IMG_1269.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B18" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="C18" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B19" s="5" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Bent Knee Vertical\IMG_1271.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B19" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="C19" s="4">
         <v>5.5</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B20" s="5" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Bent Knee Vertical\IMG_1274.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B20" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="C20" s="4">
         <v>5.7</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="5" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Bent Knee Vertical\IMG_1278.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B21" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="C21" s="4">
         <v>6.5</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="5" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Bent Knee Vertical\IMG_1279.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B22" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="C22" s="4">
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B23" s="5" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Bent Knee Vertical\IMG_1281.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B23" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="C23" s="4">
         <v>7.4</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="5" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Bent Knee Vertical\IMG_1304.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B24" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="C24" s="4">
         <v>4.5</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="5" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Bent Knee Vertical\IMG_1306.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B25" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="C25" s="4">
         <v>4.2</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B26" s="5" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Bent Knee Vertical\IMG_1311.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B26" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="C26" s="4">
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="5" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Bent Knee Vertical\IMG_1313.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B27" s="5" t="s">
+        <v>33</v>
       </c>
       <c r="C27" s="4">
         <v>6.2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A28" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B28" s="5" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Bent Knee Vertical\IMG_1316.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B28" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="C28" s="4">
         <v>6.4</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A29" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B29" s="5" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Bent Knee Vertical\IMG_1319.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B29" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="C29" s="4">
         <v>7.3</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A30" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B30" s="5" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Bent Knee Vertical\IMG_1458.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B30" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="C30" s="4">
         <v>3.5</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B31" s="5" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Bent Knee Vertical\IMG_1459.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B31" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="C31" s="4">
         <v>2.7</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A32" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B32" s="5" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Bent Knee Vertical\IMG_1463.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B32" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="C32" s="4">
         <v>5.2</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B33" s="5" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Bent Knee Vertical\IMG_1464.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B33" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="C33" s="4">
         <v>5.5</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B34" s="5" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Bent Knee Vertical\IMG_1467.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B34" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="C34" s="4">
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="6" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Double Leg Vertical\IMG_1250.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B35" s="6" t="s">
+        <v>41</v>
       </c>
       <c r="C35" s="7">
         <v>5.2</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A36" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B36" s="6" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Double Leg Vertical\IMG_1251.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B36" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="C36" s="7">
         <v>3.5</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A37" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B37" s="6" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Double Leg Vertical\IMG_1253.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B37" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="C37" s="7">
         <v>6.2</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A38" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B38" s="6" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Double Leg Vertical\IMG_1256.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B38" s="6" t="s">
+        <v>44</v>
       </c>
       <c r="C38" s="7">
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A39" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B39" s="6" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Double Leg Vertical\IMG_1257.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B39" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="C39" s="7">
         <v>5.7</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A40" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B40" s="6" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Double Leg Vertical\IMG_1260.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B40" s="6" t="s">
+        <v>46</v>
       </c>
       <c r="C40" s="7">
         <v>6.5</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A41" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B41" s="6" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Double Leg Vertical\IMG_1261.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B41" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="C41" s="7">
         <v>7.5</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A42" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B42" s="6" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Double Leg Vertical\IMG_1265.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B42" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="C42" s="7">
         <v>9.5</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A43" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B43" s="6" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Double Leg Vertical\IMG_1287.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B43" s="6" t="s">
+        <v>49</v>
       </c>
       <c r="C43" s="7">
         <v>2.5</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A44" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B44" s="6" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Double Leg Vertical\IMG_1289.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B44" s="6" t="s">
+        <v>50</v>
       </c>
       <c r="C44" s="7">
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A45" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B45" s="6" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Double Leg Vertical\IMG_1292.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B45" s="6" t="s">
+        <v>51</v>
       </c>
       <c r="C45" s="7">
         <v>3.7</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A46" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B46" s="6" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Double Leg Vertical\IMG_1294.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B46" s="6" t="s">
+        <v>52</v>
       </c>
       <c r="C46" s="7">
         <v>5.7</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A47" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B47" s="6" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Double Leg Vertical\IMG_1296.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B47" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="C47" s="7">
         <v>5.7</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A48" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B48" s="6" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Double Leg Vertical\IMG_1298.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B48" s="6" t="s">
+        <v>54</v>
       </c>
       <c r="C48" s="7">
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A49" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B49" s="6" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Double Leg Vertical\IMG_1300.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B49" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="C49" s="7">
         <v>6.2</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A50" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B50" s="6" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Double Leg Vertical\IMG_1443.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B50" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="C50" s="7">
         <v>2.8</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A51" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B51" s="6" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Double Leg Vertical\IMG_1448.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B51" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="C51" s="7">
         <v>4.8</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A52" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B52" s="6" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Double Leg Vertical\IMG_1449.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B52" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="C52" s="7">
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A53" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B53" s="6" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Double Leg Vertical\IMG_1451.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B53" s="6" t="s">
+        <v>59</v>
       </c>
       <c r="C53" s="7">
         <v>5.4</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A54" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B54" s="6" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Double Leg Vertical\IMG_1453.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B54" s="6" t="s">
+        <v>60</v>
       </c>
       <c r="C54" s="7">
         <v>6.6</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A55" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B55" s="8" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Fishtail\IMG_1322.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B55" s="8" t="s">
+        <v>61</v>
       </c>
       <c r="C55" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A56" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B56" s="8" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Fishtail\IMG_1325.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B56" s="8" t="s">
+        <v>62</v>
       </c>
       <c r="C56" s="9">
         <v>4</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A57" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B57" s="8" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Fishtail\IMG_1329.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B57" s="8" t="s">
+        <v>63</v>
       </c>
       <c r="C57" s="9">
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A58" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B58" s="8" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Fishtail\IMG_1330.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B58" s="8" t="s">
+        <v>64</v>
       </c>
       <c r="C58" s="9">
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A59" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B59" s="8" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Fishtail\IMG_1332.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B59" s="8" t="s">
+        <v>65</v>
       </c>
       <c r="C59" s="9">
         <v>6.5</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A60" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B60" s="8" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Fishtail\IMG_1335.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B60" s="8" t="s">
+        <v>66</v>
       </c>
       <c r="C60" s="9">
         <v>7.5</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A61" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B61" s="8" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Fishtail\IMG_1337.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B61" s="8" t="s">
+        <v>67</v>
       </c>
       <c r="C61" s="9">
         <v>8.5</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A62" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B62" s="8" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Fishtail\IMG_1345.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B62" s="8" t="s">
+        <v>68</v>
       </c>
       <c r="C62" s="9">
         <v>4.2</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A63" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B63" s="8" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Fishtail\IMG_1348.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B63" s="8" t="s">
+        <v>69</v>
       </c>
       <c r="C63" s="9">
         <v>5.2</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A64" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B64" s="8" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Fishtail\IMG_1351.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B64" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="C64" s="9">
         <v>6.6</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A65" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B65" s="8" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Fishtail\IMG_1353.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B65" s="8" t="s">
+        <v>71</v>
       </c>
       <c r="C65" s="9">
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A66" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B66" s="8" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Fishtail\IMG_1358.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B66" s="8" t="s">
+        <v>72</v>
       </c>
       <c r="C66" s="9">
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A67" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B67" s="8" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Fishtail\IMG_1477.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B67" s="8" t="s">
+        <v>73</v>
       </c>
       <c r="C67" s="9">
         <v>3.3</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A68" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B68" s="8" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Fishtail\IMG_1479.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B68" s="8" t="s">
+        <v>74</v>
       </c>
       <c r="C68" s="9">
         <v>4.5</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A69" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B69" s="8" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Fishtail\IMG_1480.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B69" s="8" t="s">
+        <v>75</v>
       </c>
       <c r="C69" s="9">
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A70" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B70" s="8" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Fishtail\IMG_1482.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B70" s="8" t="s">
+        <v>76</v>
       </c>
       <c r="C70" s="9">
         <v>6.3</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A71" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B71" s="8" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Fishtail\IMG_1484.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B71" s="8" t="s">
+        <v>77</v>
       </c>
       <c r="C71" s="9">
         <v>7</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A72" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B72" s="8" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Fishtail\IMG_1486.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B72" s="8" t="s">
+        <v>78</v>
       </c>
       <c r="C72" s="9">
         <v>6.7</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A73" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B73" s="8" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Fishtail\IMG_1487.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B73" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="C73" s="9">
         <v>7</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A74" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B74" s="8" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Fishtail\IMG_1488.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B74" s="8" t="s">
+        <v>80</v>
       </c>
       <c r="C74" s="9">
         <v>7.3</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A75" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B75" s="10" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Knight\IMG_1364.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B75" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="C75" s="11">
         <v>3</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A76" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B76" s="10" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Knight\IMG_1365.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B76" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="C76" s="11">
         <v>3.4</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A77" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B77" s="10" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Knight\IMG_1370.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B77" s="10" t="s">
+        <v>83</v>
       </c>
       <c r="C77" s="11">
         <v>5.3</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A78" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B78" s="10" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Knight\IMG_1376.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B78" s="10" t="s">
+        <v>84</v>
       </c>
       <c r="C78" s="11">
         <v>6</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A79" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B79" s="10" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Knight\IMG_1377.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B79" s="10" t="s">
+        <v>85</v>
       </c>
       <c r="C79" s="11">
         <v>6.3</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A80" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B80" s="10" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Knight\IMG_1380.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B80" s="10" t="s">
+        <v>86</v>
       </c>
       <c r="C80" s="11">
         <v>8.5</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A81" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B81" s="10" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Knight\IMG_1382.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B81" s="10" t="s">
+        <v>87</v>
       </c>
       <c r="C81" s="11">
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A82" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B82" s="10" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Knight\IMG_1386.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B82" s="10" t="s">
+        <v>88</v>
       </c>
       <c r="C82" s="11">
         <v>9.5</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A83" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B83" s="10" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Knight\IMG_1402.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B83" s="10" t="s">
+        <v>89</v>
       </c>
       <c r="C83" s="11">
         <v>2.5</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A84" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B84" s="10" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Knight\IMG_1410.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B84" s="10" t="s">
+        <v>90</v>
       </c>
       <c r="C84" s="11">
         <v>6.4</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A85" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B85" s="10" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Knight\IMG_1414.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B85" s="10" t="s">
+        <v>91</v>
       </c>
       <c r="C85" s="11">
         <v>6</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A86" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B86" s="10" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Knight\IMG_1415.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B86" s="10" t="s">
+        <v>92</v>
       </c>
       <c r="C86" s="11">
         <v>7.2</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A87" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B87" s="10" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Knight\IMG_1417.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B87" s="10" t="s">
+        <v>93</v>
       </c>
       <c r="C87" s="11">
         <v>7.4</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A88" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B88" s="10" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Knight\IMG_1492.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B88" s="10" t="s">
+        <v>94</v>
       </c>
       <c r="C88" s="11">
         <v>4.5</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A89" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B89" s="10" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Knight\IMG_1495.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B89" s="10" t="s">
+        <v>95</v>
       </c>
       <c r="C89" s="11">
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A90" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B90" s="10" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Knight\IMG_1499.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B90" s="10" t="s">
+        <v>96</v>
       </c>
       <c r="C90" s="11">
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A91" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B91" s="10" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Knight\IMG_1501.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B91" s="10" t="s">
+        <v>97</v>
       </c>
       <c r="C91" s="11">
         <v>6.5</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A92" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B92" s="10" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Knight\IMG_1505.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B92" s="10" t="s">
+        <v>98</v>
       </c>
       <c r="C92" s="11">
         <v>6.3</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A93" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B93" s="10" t="str">
-        <f>HYPERLINK("..\subset puntuacion\Knight\IMG_1506.JPG", "Ver Foto")</f>
-        <v>Ver Foto</v>
+      <c r="B93" s="10" t="s">
+        <v>99</v>
       </c>
       <c r="C93" s="11">
         <v>8.5</v>
